--- a/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/practice_start.xlsx
+++ b/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/practice_start.xlsx
@@ -1689,9 +1689,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
-    <col width="16.5" customWidth="1" min="2" max="2"/>
-    <col width="15.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="2" max="2"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Bulawayo</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Gweru</t>
         </is>
       </c>
     </row>
@@ -1802,17 +1802,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Mutare</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Masvingo</t>
         </is>
       </c>
     </row>
@@ -1874,17 +1874,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chitungwiza</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Chinhoyi</t>
         </is>
       </c>
     </row>
@@ -1921,17 +1921,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Johannesburg</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gaborone</t>
         </is>
       </c>
     </row>
@@ -1993,17 +1993,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E13" t="n">
